--- a/contenus/tab4/cap10-le-seuil-a-change.xlsx
+++ b/contenus/tab4/cap10-le-seuil-a-change.xlsx
@@ -663,9 +663,10 @@
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="8">
-        <f>SI( la question ; "À commander" ; "Stock suffisant" )</f>
-        <v/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>=SI( la question ; "À commander" ; "Stock suffisant" )</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
